--- a/forms/trg/Formulir_TRG_ermrg.xlsx
+++ b/forms/trg/Formulir_TRG_ermrg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Eng. Adi Maulana, S.T.,M.Phil.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1791,7 +1795,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D34" s="12" t="n"/>
@@ -1824,7 +1828,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D35" s="12" t="n"/>
@@ -1857,7 +1861,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D36" s="12" t="n"/>
@@ -1890,7 +1894,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D37" s="12" t="n"/>
